--- a/artfynd/S 3321-2022 artfynd.xlsx
+++ b/artfynd/S 3321-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114264447</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114264459</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114264460</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114264444</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86953493</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1347,6 +1377,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134192978</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1454,6 +1489,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69548208</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1551,6 +1591,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103257625</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,8 +1693,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111697717</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3321-2022 artfynd.xlsx
+++ b/artfynd/S 3321-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,56 +1144,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>86953493</v>
+        <v>136137201</v>
       </c>
       <c r="B6" t="n">
-        <v>58212</v>
+        <v>58238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102981</v>
+        <v>102980</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>föda åt ungar</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slussen, Vstm</t>
+          <t>Hjälmare docka, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553587</v>
+        <v>553559</v>
       </c>
       <c r="R6" t="n">
-        <v>6582974</v>
+        <v>6582942</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,27 +1217,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-07-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Runt 5 fågelbon totalt med fågelungar i alla.</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,75 +1247,70 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Gruvnäs</t>
+          <t>Susanne Fröjdendal</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Gruvnäs</t>
+          <t>Susanne Fröjdendal</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86953493</t>
+          <t>https://artportalen.se/Sighting/136137201</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134192978</v>
+        <v>86953493</v>
       </c>
       <c r="B7" t="n">
-        <v>56904</v>
+        <v>58212</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208255</v>
+        <v>102981</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>vilande</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vallby, Vstm</t>
+          <t>Slussen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553628</v>
+        <v>553587</v>
       </c>
       <c r="R7" t="n">
-        <v>6583104</v>
+        <v>6582974</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,12 +1337,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Runt 5 fågelbon totalt med fågelungar i alla.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,34 +1366,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Frida Olsson</t>
+          <t>Amanda Gruvnäs</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Frida Olsson</t>
+          <t>Amanda Gruvnäs</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134192978</t>
+          <t>https://artportalen.se/Sighting/86953493</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>69548208</v>
+        <v>136137202</v>
       </c>
       <c r="B8" t="n">
-        <v>98695</v>
+        <v>58570</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,42 +1400,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219606</v>
+        <v>102987</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pilblad</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sagittaria sagittifolia</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hjälmare docka, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553568</v>
+        <v>553559</v>
       </c>
       <c r="R8" t="n">
-        <v>6582931</v>
+        <v>6582942</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,12 +1458,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2009-06-20</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2009-06-20</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,74 +1484,82 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>I sötvatten</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Susanne Fröjdendal</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Susanne Fröjdendal</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69548208</t>
+          <t>https://artportalen.se/Sighting/136137202</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103257625</v>
+        <v>134192978</v>
       </c>
       <c r="B9" t="n">
-        <v>106813</v>
+        <v>56904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>208255</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hjälmare docka, Vstm</t>
+          <t>Vallby, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553703</v>
+        <v>553628</v>
       </c>
       <c r="R9" t="n">
-        <v>6583255</v>
+        <v>6583104</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1562,12 +1583,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,33 +1597,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Gunnar Björndahl</t>
+          <t>Frida Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Gunnar Björndahl</t>
+          <t>Frida Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103257625</t>
+          <t>https://artportalen.se/Sighting/134192978</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111697717</v>
+        <v>69548208</v>
       </c>
       <c r="B10" t="n">
-        <v>102419</v>
+        <v>98695</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,37 +1632,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221317</v>
+        <v>219606</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Pilblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Sagittaria sagittifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hjälmare docka, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553659</v>
+        <v>553568</v>
       </c>
       <c r="R10" t="n">
-        <v>6583134</v>
+        <v>6582931</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,12 +1691,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2009-06-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2009-06-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,20 +1707,229 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>I sötvatten</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Gunnar Björndahl</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Gunnar Björndahl</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69548208</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>103257625</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hjälmare docka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>553703</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6583255</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103257625</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111697717</v>
+      </c>
+      <c r="B12" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hjälmare docka, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>553659</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6583134</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arboga</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Arboga stad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gunnar Björndahl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111697717</t>
         </is>
@@ -1710,6 +1946,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3321-2022 artfynd.xlsx
+++ b/artfynd/S 3321-2022 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>136137201</v>
       </c>
       <c r="B6" t="n">
-        <v>58238</v>
+        <v>58239</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136137202</v>
       </c>
       <c r="B8" t="n">
-        <v>58570</v>
+        <v>58571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3321-2022 artfynd.xlsx
+++ b/artfynd/S 3321-2022 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>136137201</v>
       </c>
       <c r="B6" t="n">
-        <v>58239</v>
+        <v>58243</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136137202</v>
       </c>
       <c r="B8" t="n">
-        <v>58571</v>
+        <v>58575</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/S 3321-2022 artfynd.xlsx
+++ b/artfynd/S 3321-2022 artfynd.xlsx
@@ -1147,7 +1147,7 @@
         <v>136137201</v>
       </c>
       <c r="B6" t="n">
-        <v>58243</v>
+        <v>58244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>136137202</v>
       </c>
       <c r="B8" t="n">
-        <v>58575</v>
+        <v>58576</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
